--- a/users/dev/assets/excelTemplate/datos-pages-02.xlsx
+++ b/users/dev/assets/excelTemplate/datos-pages-02.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Cobros</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>"31"</t>
+  </si>
+  <si>
+    <t>userId</t>
   </si>
 </sst>
 </file>
@@ -195,13 +198,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -484,144 +487,147 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:33" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AD2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="3" t="s">
+      <c r="AE2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="3" t="s">
+      <c r="AF2" s="2" t="s">
         <v>32</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
